--- a/Configs/GameConfig/Datas/gameplay_graph.xlsx
+++ b/Configs/GameConfig/Datas/gameplay_graph.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="21">
   <si>
     <t>##var</t>
   </si>
@@ -82,6 +82,12 @@
     <t>root_node_id</t>
   </si>
   <si>
+    <t>trigger_day</t>
+  </si>
+  <si>
+    <t>trigger_day_param</t>
+  </si>
+  <si>
     <t>##type</t>
   </si>
   <si>
@@ -91,6 +97,9 @@
     <t>string</t>
   </si>
   <si>
+    <t>bool</t>
+  </si>
+  <si>
     <t>##group</t>
   </si>
   <si>
@@ -112,7 +121,13 @@
     <t>入口节点ID</t>
   </si>
   <si>
-    <t>点击互动</t>
+    <t>测试对话</t>
+  </si>
+  <si>
+    <t>第1天</t>
+  </si>
+  <si>
+    <t>第2天</t>
   </si>
 </sst>
 </file>
@@ -741,13 +756,10 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="22" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="23" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -1078,97 +1090,150 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E6"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="5" outlineLevelCol="4"/>
+  <dimension ref="A1:G8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="7" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="1" width="9.225" customWidth="1"/>
     <col min="2" max="2" width="9.625" style="3" customWidth="1"/>
     <col min="3" max="3" width="14.75" customWidth="1"/>
-    <col min="4" max="4" width="31.375" customWidth="1"/>
-    <col min="5" max="5" width="14.75" style="4" customWidth="1"/>
+    <col min="4" max="4" width="17.25" customWidth="1"/>
+    <col min="5" max="5" width="14.75" style="3" customWidth="1"/>
+    <col min="6" max="6" width="14.375" style="3" customWidth="1"/>
+    <col min="7" max="7" width="16.75" style="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" spans="1:5">
-      <c r="A1" s="5" t="s">
+    <row r="1" s="1" customFormat="1" spans="1:7">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="E1" s="5" t="s">
         <v>4</v>
       </c>
+      <c r="F1" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="5" t="s">
+        <v>6</v>
+      </c>
     </row>
-    <row r="2" s="1" customFormat="1" spans="1:5">
-      <c r="A2" s="5" t="s">
+    <row r="2" s="1" customFormat="1" spans="1:7">
+      <c r="A2" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="6"/>
-      <c r="C2" s="5"/>
-      <c r="D2" s="5"/>
-      <c r="E2" s="6"/>
+      <c r="B2" s="5"/>
+      <c r="C2" s="4"/>
+      <c r="D2" s="4"/>
+      <c r="E2" s="5"/>
+      <c r="F2" s="5"/>
+      <c r="G2" s="5"/>
     </row>
-    <row r="3" s="2" customFormat="1" spans="1:5">
-      <c r="A3" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="B3" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="C3" s="7" t="s">
+    <row r="3" s="2" customFormat="1" spans="1:7">
+      <c r="A3" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="D3" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="E3" s="8" t="s">
-        <v>7</v>
+      <c r="B3" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E3" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="F3" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="G3" s="7" t="s">
+        <v>8</v>
       </c>
     </row>
-    <row r="4" s="2" customFormat="1" spans="1:5">
-      <c r="A4" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4" s="8"/>
-      <c r="C4" s="7"/>
-      <c r="D4" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="E4" s="8"/>
+    <row r="4" s="2" customFormat="1" spans="1:7">
+      <c r="A4" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" s="7"/>
+      <c r="C4" s="6"/>
+      <c r="D4" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="E4" s="7"/>
+      <c r="F4" s="7"/>
+      <c r="G4" s="7"/>
     </row>
-    <row r="5" s="1" customFormat="1" spans="1:5">
-      <c r="A5" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="B5" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="D5" s="5" t="s">
+    <row r="5" s="1" customFormat="1" spans="1:7">
+      <c r="A5" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="E5" s="6" t="s">
+      <c r="B5" s="5" t="s">
         <v>14</v>
       </c>
+      <c r="C5" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="F5" s="5"/>
+      <c r="G5" s="5"/>
     </row>
     <row r="6" spans="2:5">
       <c r="B6" s="3">
+        <v>10000</v>
+      </c>
+      <c r="C6" t="s">
+        <v>18</v>
+      </c>
+      <c r="E6" s="3">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="7" spans="2:7">
+      <c r="B7" s="3">
         <v>10001</v>
       </c>
-      <c r="C6" t="s">
-        <v>15</v>
-      </c>
-      <c r="D6"/>
-      <c r="E6" s="4">
+      <c r="C7" t="s">
+        <v>19</v>
+      </c>
+      <c r="E7" s="3">
         <v>10001</v>
+      </c>
+      <c r="F7" s="3">
+        <v>1</v>
+      </c>
+      <c r="G7" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" customFormat="1" spans="2:7">
+      <c r="B8" s="3">
+        <v>10002</v>
+      </c>
+      <c r="C8" t="s">
+        <v>20</v>
+      </c>
+      <c r="E8" s="3">
+        <v>10002</v>
+      </c>
+      <c r="F8" s="3">
+        <v>1</v>
+      </c>
+      <c r="G8" s="3">
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/Configs/GameConfig/Datas/gameplay_graph.xlsx
+++ b/Configs/GameConfig/Datas/gameplay_graph.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="22">
   <si>
     <t>##var</t>
   </si>
@@ -128,6 +128,9 @@
   </si>
   <si>
     <t>第2天</t>
+  </si>
+  <si>
+    <t>饿</t>
   </si>
 </sst>
 </file>
@@ -1090,8 +1093,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G8"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="7" outlineLevelCol="6"/>
+  <dimension ref="A1:G9"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="1" width="9.225" customWidth="1"/>
     <col min="2" max="2" width="9.625" style="3" customWidth="1"/>
@@ -1236,6 +1239,17 @@
         <v>2</v>
       </c>
     </row>
+    <row r="9" spans="2:5">
+      <c r="B9" s="3">
+        <v>20001</v>
+      </c>
+      <c r="C9" t="s">
+        <v>21</v>
+      </c>
+      <c r="E9" s="3">
+        <v>20001</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
